--- a/CFOP.xlsx
+++ b/CFOP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4f184f8a7ab6e85d/Documentos/Códigos/d12/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rodrigo.correia\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="34" documentId="13_ncr:1_{CBF38701-D345-420B-A42C-DB78641699BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B028C4C6-3FD3-4DEC-9D22-3C140BDC4BB0}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{871EFC2E-2E5A-4E2E-B2AD-958328BCEA43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0BEBC162-6D48-49B9-BA73-51267E561D70}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{0BEBC162-6D48-49B9-BA73-51267E561D70}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="33">
   <si>
     <t>cfop</t>
   </si>
@@ -161,7 +161,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -171,6 +171,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -202,7 +208,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -217,6 +223,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -241,9 +250,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office 2013 - 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -281,7 +290,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -387,7 +396,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -529,7 +538,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -537,21 +546,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2543010-56E5-4463-A5FB-C7CAE9F50499}">
-  <dimension ref="A1:C84"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:C93"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="28.109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="39.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="41.44140625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="6.88671875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="6.109375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="41.44140625" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="6.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="28.140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="39.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="41.42578125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="6.85546875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="6.140625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="41.42578125" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -562,7 +571,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>1253</v>
       </c>
@@ -573,7 +582,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>1303</v>
       </c>
@@ -584,7 +593,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>1407</v>
       </c>
@@ -595,7 +604,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>1556</v>
       </c>
@@ -606,7 +615,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>1653</v>
       </c>
@@ -617,7 +626,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>2253</v>
       </c>
@@ -628,7 +637,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>2407</v>
       </c>
@@ -639,7 +648,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>2556</v>
       </c>
@@ -650,7 +659,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>2653</v>
       </c>
@@ -661,7 +670,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>1406</v>
       </c>
@@ -672,7 +681,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <v>1551</v>
       </c>
@@ -683,7 +692,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>2551</v>
       </c>
@@ -694,7 +703,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <v>5927</v>
       </c>
@@ -705,7 +714,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <v>1910</v>
       </c>
@@ -716,7 +725,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <v>2910</v>
       </c>
@@ -727,7 +736,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>6910</v>
       </c>
@@ -738,7 +747,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
         <v>1922</v>
       </c>
@@ -749,7 +758,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>1202</v>
       </c>
@@ -760,7 +769,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
         <v>1411</v>
       </c>
@@ -771,7 +780,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>2202</v>
       </c>
@@ -782,7 +791,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
         <v>2411</v>
       </c>
@@ -793,7 +802,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <v>5202</v>
       </c>
@@ -804,7 +813,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
         <v>5411</v>
       </c>
@@ -815,7 +824,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
         <v>5603</v>
       </c>
@@ -826,7 +835,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
         <v>6202</v>
       </c>
@@ -837,7 +846,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
         <v>6411</v>
       </c>
@@ -848,7 +857,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
         <v>6603</v>
       </c>
@@ -859,7 +868,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
         <v>1201</v>
       </c>
@@ -870,7 +879,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="4">
         <v>2201</v>
       </c>
@@ -881,7 +890,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
         <v>5201</v>
       </c>
@@ -892,7 +901,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
         <v>2353</v>
       </c>
@@ -903,7 +912,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
         <v>2932</v>
       </c>
@@ -914,7 +923,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
         <v>1101</v>
       </c>
@@ -925,7 +934,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
         <v>1116</v>
       </c>
@@ -936,7 +945,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
         <v>1352</v>
       </c>
@@ -947,7 +956,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
         <v>2101</v>
       </c>
@@ -958,7 +967,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
         <v>2352</v>
       </c>
@@ -969,7 +978,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
         <v>5101</v>
       </c>
@@ -980,7 +989,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
         <v>6101</v>
       </c>
@@ -991,7 +1000,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
         <v>6107</v>
       </c>
@@ -1002,7 +1011,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="5">
         <v>5117</v>
       </c>
@@ -1013,7 +1022,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="5">
         <v>6117</v>
       </c>
@@ -1024,7 +1033,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="4">
         <v>5116</v>
       </c>
@@ -1035,7 +1044,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
         <v>6116</v>
       </c>
@@ -1046,7 +1055,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="5">
         <v>1908</v>
       </c>
@@ -1057,7 +1066,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="5">
         <v>1914</v>
       </c>
@@ -1068,7 +1077,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="5">
         <v>1916</v>
       </c>
@@ -1079,7 +1088,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="5">
         <v>1926</v>
       </c>
@@ -1090,7 +1099,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="5">
         <v>1933</v>
       </c>
@@ -1101,7 +1110,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="5">
         <v>1949</v>
       </c>
@@ -1112,7 +1121,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="5">
         <v>2449</v>
       </c>
@@ -1123,7 +1132,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="5">
         <v>2908</v>
       </c>
@@ -1134,7 +1143,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="5">
         <v>2911</v>
       </c>
@@ -1145,7 +1154,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="5">
         <v>2916</v>
       </c>
@@ -1156,7 +1165,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="5">
         <v>2920</v>
       </c>
@@ -1167,7 +1176,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="5">
         <v>2923</v>
       </c>
@@ -1178,7 +1187,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="5">
         <v>2926</v>
       </c>
@@ -1189,7 +1198,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="5">
         <v>2949</v>
       </c>
@@ -1200,7 +1209,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="5">
         <v>5910</v>
       </c>
@@ -1211,7 +1220,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="5">
         <v>5914</v>
       </c>
@@ -1222,7 +1231,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="5">
         <v>5915</v>
       </c>
@@ -1233,7 +1242,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="5">
         <v>5921</v>
       </c>
@@ -1244,7 +1253,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="5">
         <v>5926</v>
       </c>
@@ -1255,7 +1264,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="5">
         <v>5949</v>
       </c>
@@ -1266,7 +1275,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="5">
         <v>6949</v>
       </c>
@@ -1277,7 +1286,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="4">
         <v>6915</v>
       </c>
@@ -1288,7 +1297,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="5">
         <v>5922</v>
       </c>
@@ -1299,7 +1308,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="5">
         <v>6922</v>
       </c>
@@ -1310,7 +1319,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="5">
         <v>1102</v>
       </c>
@@ -1321,7 +1330,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="5">
         <v>1353</v>
       </c>
@@ -1332,7 +1341,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="5">
         <v>1403</v>
       </c>
@@ -1343,7 +1352,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="5">
         <v>1652</v>
       </c>
@@ -1354,7 +1363,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="5">
         <v>2102</v>
       </c>
@@ -1365,7 +1374,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="5">
         <v>2403</v>
       </c>
@@ -1376,7 +1385,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="5">
         <v>5102</v>
       </c>
@@ -1387,7 +1396,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="5">
         <v>5353</v>
       </c>
@@ -1398,7 +1407,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="5">
         <v>5403</v>
       </c>
@@ -1409,7 +1418,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="5">
         <v>5405</v>
       </c>
@@ -1420,7 +1429,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="5">
         <v>5656</v>
       </c>
@@ -1431,7 +1440,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="5">
         <v>6102</v>
       </c>
@@ -1442,7 +1451,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="5">
         <v>6108</v>
       </c>
@@ -1453,7 +1462,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="5">
         <v>6360</v>
       </c>
@@ -1464,7 +1473,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="5">
         <v>6932</v>
       </c>
@@ -1473,6 +1482,105 @@
       </c>
       <c r="C84" s="5" t="s">
         <v>16</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="1">
+        <v>1415</v>
+      </c>
+      <c r="B85" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="1">
+        <v>1904</v>
+      </c>
+      <c r="B86" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" s="6">
+        <v>2122</v>
+      </c>
+      <c r="B87" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" s="6">
+        <v>2125</v>
+      </c>
+      <c r="B88" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" s="6">
+        <v>2925</v>
+      </c>
+      <c r="B89" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" s="1">
+        <v>5103</v>
+      </c>
+      <c r="B90" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" s="1">
+        <v>5104</v>
+      </c>
+      <c r="B91" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="1">
+        <v>5415</v>
+      </c>
+      <c r="B92" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" s="1">
+        <v>5904</v>
+      </c>
+      <c r="B93" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/CFOP.xlsx
+++ b/CFOP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rodrigo.correia\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{871EFC2E-2E5A-4E2E-B2AD-958328BCEA43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ADA3E37-55B4-46EC-B53C-E05D9714C8FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{0BEBC162-6D48-49B9-BA73-51267E561D70}"/>
   </bookViews>
@@ -30,8 +30,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -39,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="34">
   <si>
     <t>cfop</t>
   </si>
@@ -138,6 +136,9 @@
   </si>
   <si>
     <t>anotar despesas (comercio)</t>
+  </si>
+  <si>
+    <t>serv. 3°</t>
   </si>
 </sst>
 </file>
@@ -161,7 +162,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -174,14 +175,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -204,11 +199,37 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -225,14 +246,44 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -546,10 +597,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2543010-56E5-4463-A5FB-C7CAE9F50499}">
-  <dimension ref="A1:C93"/>
+  <dimension ref="A1:C98"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="16" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28.140625" style="1" customWidth="1"/>
     <col min="3" max="3" width="39.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.140625" style="1" customWidth="1"/>
@@ -1474,7 +1525,7 @@
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" s="5">
+      <c r="A84" s="9">
         <v>6932</v>
       </c>
       <c r="B84" s="5" t="s">
@@ -1485,32 +1536,32 @@
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" s="1">
+      <c r="A85" s="6">
         <v>1415</v>
       </c>
-      <c r="B85" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C85" s="4" t="s">
-        <v>29</v>
+      <c r="B85" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C85" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" s="1">
+      <c r="A86" s="6">
         <v>1904</v>
       </c>
-      <c r="B86" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C86" s="4" t="s">
-        <v>29</v>
+      <c r="B86" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C86" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="6">
         <v>2122</v>
       </c>
-      <c r="B87" s="5" t="s">
+      <c r="B87" s="7" t="s">
         <v>31</v>
       </c>
       <c r="C87" s="4" t="s">
@@ -1521,7 +1572,7 @@
       <c r="A88" s="6">
         <v>2125</v>
       </c>
-      <c r="B88" s="5" t="s">
+      <c r="B88" s="7" t="s">
         <v>31</v>
       </c>
       <c r="C88" s="4" t="s">
@@ -1532,7 +1583,7 @@
       <c r="A89" s="6">
         <v>2925</v>
       </c>
-      <c r="B89" s="5" t="s">
+      <c r="B89" s="7" t="s">
         <v>28</v>
       </c>
       <c r="C89" s="4" t="s">
@@ -1540,10 +1591,10 @@
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" s="1">
+      <c r="A90" s="6">
         <v>5103</v>
       </c>
-      <c r="B90" s="5" t="s">
+      <c r="B90" s="7" t="s">
         <v>31</v>
       </c>
       <c r="C90" s="4" t="s">
@@ -1551,36 +1602,91 @@
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91" s="1">
+      <c r="A91" s="6">
         <v>5104</v>
       </c>
-      <c r="B91" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C91" s="4" t="s">
-        <v>17</v>
+      <c r="B91" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C91" s="5" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92" s="1">
+      <c r="A92" s="6">
         <v>5415</v>
       </c>
-      <c r="B92" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C92" s="4" t="s">
-        <v>29</v>
+      <c r="B92" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C92" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93" s="1">
+      <c r="A93" s="6">
         <v>5904</v>
       </c>
-      <c r="B93" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C93" s="4" t="s">
-        <v>29</v>
+      <c r="B93" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C93" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" s="6">
+        <v>1126</v>
+      </c>
+      <c r="B94" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C94" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" s="6">
+        <v>1912</v>
+      </c>
+      <c r="B95" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C95" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" s="6">
+        <v>2121</v>
+      </c>
+      <c r="B96" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C96" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" s="6">
+        <v>2933</v>
+      </c>
+      <c r="B97" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C97" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="6">
+        <v>5913</v>
+      </c>
+      <c r="B98" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C98" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
